--- a/outputs/evaluation/architecture/CF_M05_arch_eval_llm_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M05_arch_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,7 +496,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The end user of the system, including business users, support staff, and administrators.</t>
+          <t>The end user of the portal and applications.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -525,312 +525,508 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.0433</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_09</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>AU_07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Amazon Web Services (AWS)</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Connection between User and Internet.</t>
+          <t>Cloud provider hosting the system infrastructure.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>AU_01, AU_10</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>user, internet</t>
-        </is>
-      </c>
+          <t>60, 81</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CF_M05_AU28</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>CF_M05_AU10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ViewModel acts as an intermediary between the View and the Model </t>
+          <t xml:space="preserve"> the microservices are connected to a shared database (Amazon RDS) that is decoupled per
+microservice and client. </t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.2166</v>
+        <v>0.3794</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Server Layer (Backend)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Network medium for user access.</t>
+          <t>Handles business logic, security, and data persistence.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>AU_09</t>
-        </is>
-      </c>
+          <t>61, 68</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CF_M05_AU28</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>CF_M05_AU37</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ViewModel acts as an intermediary between the View and the Model </t>
+          <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
+responsibilities are separated:</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.1109</v>
+        <v>0.3573</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_11</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Controller</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Connection between Internet and Portal Gateway.</t>
+          <t>Handles REST API requests and responses.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU_10, AU_03</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>internet, portal</t>
-        </is>
-      </c>
+          <t>AU_14</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CF_M05_AU02</t>
+          <t>CF_M05_AU17</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Portal Microservice</t>
+          <t>Presentation Layer (Controllers)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">The portal microservice's main function is to provide a centralized interface for accessing the different VWGS
-applications. This component acts as an entry point for users, providing a unified experience. In addition to its
-function as a portal, this microservice incorporates the necessary binaries for the frontEnd of both the portal
-itself and the rest of the portal's applications. </t>
+          <t>The controllers, through specific
+functions, process the requests received, manage the validation of the information and channel
+the requests to the corresponding modules or services of the data layer.</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.2336</v>
+        <v>0.4133</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>AU_18</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DTO / Mapper</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Handles data transfer objects and conversion between models and external representations.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>AU_14</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Connection between internal microservices and Amazon RDS.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>AU_04, AU_07</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>access control, amazon rds</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
+          <t>CF_M05_AU20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Contract Layer (DTO/Mappers)</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Data Transfer Objects (DTOs) act as information containers that allow the data required for each
+request to be structured, providing a customized format based on response requirements.</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.2503</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AU_22</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>The User communicates with the Portal Service via the internet.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>AU_01, AU_03</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>user, portal service</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>CF_M05_AU27</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Portal microservice communicates with the frontend indirectly through the Leader microservice</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.3682</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AU_26</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>The Leader Service communicates with the Communication Log Service.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>56, 58</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>AU_02, AU_05</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>leader service, communication log service</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>CF_M05_AU25</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">It can be observed that leader microservice communicates with Communication Log microservice. </t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0.6552</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AU_27</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>The Leader Service communicates with the Portal Service.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>56, 57</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>AU_02, AU_03</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>leader service, portal service</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>CF_M05_AU23</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">It can be observed that leader microservice communicates with Portal microservice. </t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0.5642</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AU_28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>The Scheduler Service communicates with Amazon RDS for data persistence.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>AU_06, AU_09</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>scheduler service, amazon rds</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>CF_M05_AU10</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Amazon RDS</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve"> the microservices are connected to a shared database (Amazon RDS) that is decoupled per
 microservice and client. </t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>0.5413</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>AU_27</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Data format for communication.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>AU_13</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>CF_M05_AU08</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>SonarQube</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>SonarQube is a
-web application that statically analyses the code and offers recommendations and statistics
-on the results. The results also detect bugs, security vulnerabilities, maintainability
-problems, the amount of code covered in the tests, code duplication and code smells.</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>0.0604</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>P_06</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Single-Page Application (SPA)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>The client is developed as a Single-Page Application that renders dynamic views and manages internal navigation without reloading the page.</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
+      <c r="L10" t="n">
+        <v>0.4667</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AU_29</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>The Access Control Service communicates with Amazon RDS for data persistence.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>AU_04, AU_09</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>access control service, amazon rds</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>CF_M05_AU03</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Access Control Microservice</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The main objective of the Access Control microservice is to manage user authentication and
+permissions within the application. </t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.4402</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AU_30</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>The Communication Log Service communicates with Amazon RDS for data persistence.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>AU_05, AU_09</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>communication log service, amazon rds</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
         <is>
           <t>CF_M05_AU04</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Communication Log Microservice</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>The main purpose of the Communication Log microservice is to record all
 communications that occur within the system, both between microservices and with external
@@ -840,8 +1036,430 @@
 and faster analysis.</t>
         </is>
       </c>
-      <c r="L8" t="n">
-        <v>0.1552</v>
+      <c r="L12" t="n">
+        <v>0.5246</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AU_31</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>The Portal Service communicates with Amazon RDS for data persistence.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>AU_03, AU_09</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>portal service, amazon rds</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>CF_M05_AU10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> the microservices are connected to a shared database (Amazon RDS) that is decoupled per
+microservice and client. </t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.4757</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AU_32</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>The Presentation Layer communicates with the ViewModel component.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>61, 64</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>AU_10, AU_12</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>presentation layer (frontend), viewmodel</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CF_M05_AU17</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Presentation Layer (Controllers)</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>The controllers, through specific
+functions, process the requests received, manage the validation of the information and channel
+the requests to the corresponding modules or services of the data layer.</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.4574</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AU_34</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>The ViewModel component sends HTTP requests to the Controller component.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>64, 68</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>AU_12, AU_15</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>viewmodel, controller</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>CF_M05_AU30</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>The controllers, through specific
+functions, process the requests received, manage the validation of the information and channel
+the requests to the corresponding modules or services</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.3278</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AU_35</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>The Controller component communicates with the Service (Backend) component.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>68, 70</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>AU_15, AU_16</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>controller, service (backend)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>CF_M05_AU37</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
+responsibilities are separated:</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0.2506</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AU_36</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>The Service (Backend) component communicates with the Repository component.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>70, 74</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>AU_16, AU_19</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>service (backend), repository</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>CF_M05_AU37</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
+responsibilities are separated:</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0.2506</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AU_37</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>The Repository component communicates with the Model (Backend) component.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>AU_19, AU_17</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>repository, model (backend)</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>CF_M05_AU15</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Models are the TypeScript classes that define the data contract consumed by the
+view and the ViewModel. These classes allow the View to know what data to display and
+the ViewModel to know how to manipulate it</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>0.2469</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AU_38</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>The Service (Backend) component communicates with the DTO / Mapper component.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>AU_16, AU_18</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>service (backend), dto / mapper</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>CF_M05_AU25</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">It can be observed that leader microservice communicates with Communication Log microservice. </t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>0.2349</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>P_06</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Single-Page Application (SPA)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>The client is developed as a Single-Page Application that renders dynamic views and manages internal navigation without reloading the page.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>P_03</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>CF_M05_AU04</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Communication Log Microservice</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>The main purpose of the Communication Log microservice is to record all
+communications that occur within the system, both between microservices and with external
+services. This component acts as a traceability and audit mechanism, ensuring that each
+interaction is documented for later analysis, incident resolution and regulatory compliance. In addition, it offers the functionality to generate graphs and interactive panels that represent
+communication statistics, traffic volume, response times and incidents, facilitating more intuitive
+and faster analysis.</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>0.1559</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M05_arch_eval_llm_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M05_arch_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,215 +481,220 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>JSON</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The end user of the portal and applications.</t>
+          <t>El format de dades emprat és JSON.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>9, 47</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>P_03</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CF_M05_AU01</t>
+          <t>CF_M05_AU31</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Leader Microservice</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>This microservice has as its main function the routing of all communications to the corresponding microservice
-within the system architecture. It acts as a central point for traffic management, ensuring that any interaction,
-both with external services and between internal microservices, is carried out in an orderly and secure manner.</t>
+          <t>The message
+exchange protocol used in this case is HTTP</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.0343</v>
+        <v>0.678</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_19</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Capa de presentació</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>The User communicates with the Portal Service via the internet.</t>
+          <t>La capa de presentació rep les peticions i construeix les respostes.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_01, AU_03</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>user, portal service</t>
-        </is>
-      </c>
+          <t>P_05</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CF_M05_AU27</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>CF_M05_AU17</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Presentation Layer (Controllers)</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Portal microservice communicates with the frontend indirectly through the Leader microservice</t>
+          <t>The controllers, through specific
+functions, process the requests received, manage the validation of the information and channel
+the requests to the corresponding modules or services of the data layer.</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.4143</v>
+        <v>0.701</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_22</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>AU_18</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Capa de domini</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>The Leader Service routes communications to the Communication Log Service.</t>
+          <t>La capa de domini defineix el model de dades.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>57, 60</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_02, AU_05</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>leader service, communication log service</t>
-        </is>
-      </c>
+          <t>P_05</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CF_M05_AU04</t>
+          <t>CF_M05_AU19</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Communication Log Microservice</t>
+          <t>Domain Layer (Models)</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>The main purpose of the Communication Log microservice is to record all
-communications that occur within the system, both between microservices and with external
-services. This component acts as a traceability and audit mechanism, ensuring that each
-interaction is documented for later analysis, incident resolution and regulatory compliance. In addition, it offers the functionality to generate graphs and interactive panels that represent
-communication statistics, traffic volume, response times and incidents, facilitating more intuitive
-and faster analysis.</t>
+          <t>Models represent the internal and persistent structure of the system entities, reflecting the
+stored information identically.</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.6661</v>
+        <v>0.6918</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_24</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>AU_19</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Capa de contracte</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>The Scheduler Service reads from and writes to Amazon RDS.</t>
+          <t>S’hi afegeix una capa transversal de contracte que separa el model intern de la representació externa de l’API.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU_06, AU_08</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>scheduler service, amazon rds</t>
-        </is>
-      </c>
+          <t>P_05</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CF_M05_AU10</t>
+          <t>CF_M05_AU20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Amazon RDS</t>
+          <t>Contract Layer (DTO/Mappers)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> the microservices are connected to a shared database (Amazon RDS) that is decoupled per
-microservice and client. </t>
+          <t>Data Transfer Objects (DTOs) act as information containers that allow the data required for each
+request to be structured, providing a customized format based on response requirements.</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.476</v>
+        <v>0.6848</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -700,49 +705,49 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>The Access Control Service reads from and writes to Amazon RDS.</t>
+          <t>El client s’ha desenvolupat amb Angular, implementant una Single-Page Application (SPA). [...] El protocol d’intercanvi de missatges que es fa servir en aquest cas és HTTP. [...] El format de dades emprat és JSON.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AU_04, AU_08</t>
+          <t>AU_08, AU_09, AU_10, AU_11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>access control service, amazon rds</t>
+          <t>angular, spring boot, http, json</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CF_M05_AU03</t>
+          <t>CF_M05_AU31</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Access Control Microservice</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">The main objective of the Access Control microservice is to manage user authentication and
-permissions within the application. </t>
+          <t>The message
+exchange protocol used in this case is HTTP</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.4672</v>
+        <v>0.7181999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_26</t>
+          <t>AU_24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -753,53 +758,49 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>The Communication Log Service reads from and writes to Amazon RDS.</t>
+          <t>La capa de presentació rep les peticions i construeix les respostes, la capa de lògica de negoci aplica les regles del domini, la capa d’accés a dades interactua amb la base de dades i la capa de domini defineix el model de dades. S’hi afegeix una capa transversal de contracte que separa el model intern de la representació externa de l’API.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_05, AU_08</t>
+          <t>AU_15, AU_16, AU_17, AU_18, AU_19</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>communication log service, amazon rds</t>
+          <t>capa de presentació, capa de lògica de negoci, capa d’accés a dades, capa de domini, capa de contracte</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CF_M05_AU04</t>
+          <t>CF_M05_AU19</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Communication Log Microservice</t>
+          <t>Domain Layer (Models)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>The main purpose of the Communication Log microservice is to record all
-communications that occur within the system, both between microservices and with external
-services. This component acts as a traceability and audit mechanism, ensuring that each
-interaction is documented for later analysis, incident resolution and regulatory compliance. In addition, it offers the functionality to generate graphs and interactive panels that represent
-communication statistics, traffic volume, response times and incidents, facilitating more intuitive
-and faster analysis.</t>
+          <t>Models represent the internal and persistent structure of the system entities, reflecting the
+stored information identically.</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.4829</v>
+        <v>0.7736</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_27</t>
+          <t>AU_25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -810,7 +811,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>The Portal Service reads from and writes to Amazon RDS.</t>
+          <t>En cada portal es realitzen els controls d’autentificació i autorització pertinents amb ajuda del Leader el qual decideix a quin domini funcional s’ha d’encaminar cada usuari.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -820,39 +821,34 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AU_03, AU_08</t>
+          <t>AU_02, AU_01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>portal service, amazon rds</t>
+          <t>portal, leader</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CF_M05_AU10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Amazon RDS</t>
-        </is>
-      </c>
+          <t>CF_M05_AU22</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> the microservices are connected to a shared database (Amazon RDS) that is decoupled per
-microservice and client. </t>
+          <t>Leader's main function is to route all communications to the corresponding microservice within the system architecture.</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.4825</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_29</t>
+          <t>AU_26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -863,257 +859,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>The ViewModel orchestrates HTTP calls to the backend Presentation Layer.</t>
+          <t>Aquest microservei té com a funció principal l’encaminament de totes les comunicacions cap al microservei corresponent dins de l’arquitectura del sistema. [...] Actua com a punt central de gestió del trànsit, garantint que qualsevol interacció, tant amb serveis externs com entre microserveis interns, es realitzi de manera ordenada i segura.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AU_12, AU_14</t>
+          <t>AU_01, AU_03, AU_04, AU_05, AU_06, AU_07</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>viewmodel, presentation layer (controller)</t>
+          <t>leader, access control, communication log, scheduler, ordering, gsb</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CF_M05_AU14</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>ViewModel</t>
-        </is>
-      </c>
+          <t>CF_M05_AU22</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>The ViewModel component groups the TS files of the components and the services they
-have associated with them. Each TS file defines the behavior of the application component
-to which it corresponds, taking care of data processing and validations</t>
+          <t>Leader's main function is to route all communications to the corresponding microservice within the system architecture.</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.3219</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>AU_30</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>The Presentation Layer communicates with the Business Logic Layer.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>68, 70</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>AU_14, AU_15</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>presentation layer (controller), business logic layer (service)</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>CF_M05_AU18</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Business Logic Layer (Services)</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Services provide the interface and implementation of all the application's business logic.</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>0.5426</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>AU_31</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>The Business Logic Layer interacts with the Data Access Layer.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>70, 74</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>AU_15, AU_18</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>business logic layer (service), data access layer (repository)</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>CF_M05_AU18</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Business Logic Layer (Services)</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Services provide the interface and implementation of all the application's business logic.</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>0.5238</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>AU_32</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>The Data Access Layer interacts with Amazon RDS.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>AU_18, AU_08</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>data access layer (repository), amazon rds</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>CF_M05_AU21</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Data access layer (Repositories)</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>the Repositories are responsible for performing queries on the database.</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>0.4864</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>P_06</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Single-Page Application (SPA)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>The client is developed as a Single-Page Application that renders dynamic views and manages internal navigation without reloading the page.</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>CF_M05_AU04</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Communication Log Microservice</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>The main purpose of the Communication Log microservice is to record all
-communications that occur within the system, both between microservices and with external
-services. This component acts as a traceability and audit mechanism, ensuring that each
-interaction is documented for later analysis, incident resolution and regulatory compliance. In addition, it offers the functionality to generate graphs and interactive panels that represent
-communication statistics, traffic volume, response times and incidents, facilitating more intuitive
-and faster analysis.</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>0.135</v>
+        <v>0.8071</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M05_arch_eval_llm_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M05_arch_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,220 +481,213 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JSON</t>
+          <t>User</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>El format de dades emprat és JSON.</t>
+          <t>The user is the actor that accesses the portal and applications.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CF_M05_AU31</t>
+          <t>CF_M05_AU13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>View</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>The message
-exchange protocol used in this case is HTTP</t>
+          <t>The component we call View, Vista in Catalan, is made up of the HTML and SCSS files of
+each component that makes up the application. They are responsible for presenting the
+screens and capturing user interactions such as clicks or text entries.</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.678</v>
+        <v>0.7551</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capa de presentació</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>La capa de presentació rep les peticions i construeix les respostes.</t>
+          <t>The administrator is a user with additional permissions to manage application access.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>P_05</t>
-        </is>
-      </c>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
+          <t>CF_M05_AU32</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Server (Backend)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
+responsibilities are separated:</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.6979</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AU_16</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Controller</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Controllers process received requests, manage validation, and channel requests to the data layer.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>AU_03, P_05</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>CF_M05_AU17</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Presentation Layer (Controllers)</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>The controllers, through specific
 functions, process the requests received, manage the validation of the information and channel
 the requests to the corresponding modules or services of the data layer.</t>
         </is>
       </c>
-      <c r="L3" t="n">
-        <v>0.701</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AU_18</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Capa de domini</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>La capa de domini defineix el model de dades.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>P_05</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>CF_M05_AU19</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Domain Layer (Models)</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Models represent the internal and persistent structure of the system entities, reflecting the
-stored information identically.</t>
-        </is>
-      </c>
       <c r="L4" t="n">
-        <v>0.6918</v>
+        <v>0.7563</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capa de contracte</t>
+          <t>JSON</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>S’hi afegeix una capa transversal de contracte que separa el model intern de la representació externa de l’API.</t>
+          <t>Data format used for message exchange.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>61</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>P_05</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CF_M05_AU20</t>
+          <t>CF_M05_AU31</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Contract Layer (DTO/Mappers)</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Data Transfer Objects (DTOs) act as information containers that allow the data required for each
-request to be structured, providing a customized format based on response requirements.</t>
+          <t>The message
+exchange protocol used in this case is HTTP</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.6848</v>
+        <v>0.678</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>AU_24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -705,49 +698,51 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>El client s’ha desenvolupat amb Angular, implementant una Single-Page Application (SPA). [...] El protocol d’intercanvi de missatges que es fa servir en aquest cas és HTTP. [...] El format de dades emprat és JSON.</t>
+          <t>The user accesses the portal and applications.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AU_08, AU_09, AU_10, AU_11</t>
+          <t>AU_01, AU_09</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>angular, spring boot, http, json</t>
+          <t>user, portal</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CF_M05_AU31</t>
+          <t>CF_M05_AU02</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>Portal Microservice</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>The message
-exchange protocol used in this case is HTTP</t>
+          <t xml:space="preserve">The portal microservice's main function is to provide a centralized interface for accessing the different VWGS
+applications. This component acts as an entry point for users, providing a unified experience. In addition to its
+function as a portal, this microservice incorporates the necessary binaries for the frontEnd of both the portal
+itself and the rest of the portal's applications. </t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.7501</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_24</t>
+          <t>AU_25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -758,49 +753,44 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>La capa de presentació rep les peticions i construeix les respostes, la capa de lògica de negoci aplica les regles del domini, la capa d’accés a dades interactua amb la base de dades i la capa de domini defineix el model de dades. S’hi afegeix una capa transversal de contracte que separa el model intern de la representació externa de l’API.</t>
+          <t>The Leader microservice routes all communications to the corresponding microservice within the system architecture.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_15, AU_16, AU_17, AU_18, AU_19</t>
+          <t>AU_08, AU_09, AU_10, AU_11, AU_12</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>capa de presentació, capa de lògica de negoci, capa d’accés a dades, capa de domini, capa de contracte</t>
+          <t>leader, portal, access control, communication log, scheduler</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CF_M05_AU19</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Domain Layer (Models)</t>
-        </is>
-      </c>
+          <t>CF_M05_AU22</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Models represent the internal and persistent structure of the system entities, reflecting the
-stored information identically.</t>
+          <t>Leader's main function is to route all communications to the corresponding microservice within the system architecture.</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.7736</v>
+        <v>0.9520999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -811,44 +801,51 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>En cada portal es realitzen els controls d’autentificació i autorització pertinents amb ajuda del Leader el qual decideix a quin domini funcional s’ha d’encaminar cada usuari.</t>
+          <t>The portal microservice incorporates the binaries necessary for the frontEnd of both the portal itself and the rest of the portal applications.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AU_02, AU_01</t>
+          <t>AU_09, AU_13, AU_14, AU_15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>portal, leader</t>
+          <t>portal, view, viewmodel, model</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CF_M05_AU22</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>CF_M05_AU02</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Portal Microservice</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Leader's main function is to route all communications to the corresponding microservice within the system architecture.</t>
+          <t xml:space="preserve">The portal microservice's main function is to provide a centralized interface for accessing the different VWGS
+applications. This component acts as an entry point for users, providing a unified experience. In addition to its
+function as a portal, this microservice incorporates the necessary binaries for the frontEnd of both the portal
+itself and the rest of the portal's applications. </t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.75</v>
+        <v>0.8185</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_26</t>
+          <t>AU_28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -859,38 +856,97 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Aquest microservei té com a funció principal l’encaminament de totes les comunicacions cap al microservei corresponent dins de l’arquitectura del sistema. [...] Actua com a punt central de gestió del trànsit, garantint que qualsevol interacció, tant amb serveis externs com entre microserveis interns, es realitzi de manera ordenada i segura.</t>
+          <t>The services are responsible for orchestrating HTTP calls to the server.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AU_01, AU_03, AU_04, AU_05, AU_06, AU_07</t>
+          <t>AU_14, AU_16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>leader, access control, communication log, scheduler, ordering, gsb</t>
+          <t>viewmodel, controller</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CF_M05_AU22</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>CF_M05_AU31</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Leader's main function is to route all communications to the corresponding microservice within the system architecture.</t>
+          <t>The message
+exchange protocol used in this case is HTTP</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.8071</v>
+        <v>0.7796999999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AU_29</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Controllers process received requests, manage validation, and channel requests to the data layer.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>AU_16, AU_04</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>controller, business logic layer</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>CF_M05_AU17</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Presentation Layer (Controllers)</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>The controllers, through specific
+functions, process the requests received, manage the validation of the information and channel
+the requests to the corresponding modules or services of the data layer.</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0.7791</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M05_arch_eval_llm_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M05_arch_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,12 +481,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The user is the actor that accesses the portal and applications.</t>
+          <t>The administrator is a user with additional permissions to manage application access for users.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -509,49 +509,48 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CF_M05_AU13</t>
+          <t>CF_M05_AU32</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>Server (Backend)</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>The component we call View, Vista in Catalan, is made up of the HTML and SCSS files of
-each component that makes up the application. They are responsible for presenting the
-screens and capturing user interactions such as clicks or text entries.</t>
+          <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
+responsibilities are separated:</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.7551</v>
+        <v>0.6979</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>JSON</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>The administrator is a user with additional permissions to manage application access.</t>
+          <t>The data format used for communication.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -559,76 +558,70 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CF_M05_AU32</t>
+          <t>CF_M05_AU31</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Server (Backend)</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
-responsibilities are separated:</t>
+          <t>The message
+exchange protocol used in this case is HTTP</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.6979</v>
+        <v>0.678</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_16</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Controller</t>
-        </is>
-      </c>
+          <t>AU_20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Controllers process received requests, manage validation, and channel requests to the data layer.</t>
+          <t>The Leader microservice has as its main function the routing of all communications to the corresponding microservice within the system architecture.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_03, P_05</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>AU_08, AU_09, AU_10, AU_11, AU_12</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>leader, portal, access control, communication log, scheduler</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CF_M05_AU17</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Presentation Layer (Controllers)</t>
-        </is>
-      </c>
+          <t>CF_M05_AU22</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>The controllers, through specific
-functions, process the requests received, manage the validation of the information and channel
-the requests to the corresponding modules or services of the data layer.</t>
+          <t>Leader's main function is to route all communications to the corresponding microservice within the system architecture.</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.7563</v>
+        <v>0.9671</v>
       </c>
     </row>
     <row r="5">
@@ -637,97 +630,44 @@
           <t>AU_21</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Data format used for message exchange.</t>
+          <t>The portal microservice has as its main function to offer a centralized interface for access to the different VWGS applications. [...] This component acts as an entry point for users, providing a unified experience.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU_08</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>AU_09, AU_08, AU_10, AU_11, AU_12</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>portal, leader, access control, communication log, scheduler</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CF_M05_AU31</t>
+          <t>CF_M05_AU02</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>Portal Microservice</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
-        <is>
-          <t>The message
-exchange protocol used in this case is HTTP</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>0.678</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AU_24</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>The user accesses the portal and applications.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>AU_01, AU_09</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>user, portal</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>CF_M05_AU02</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Portal Microservice</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">The portal microservice's main function is to provide a centralized interface for accessing the different VWGS
 applications. This component acts as an entry point for users, providing a unified experience. In addition to its
@@ -735,14 +675,62 @@
 itself and the rest of the portal's applications. </t>
         </is>
       </c>
+      <c r="L5" t="n">
+        <v>0.8241000000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AU_22</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>The Communication Log microservice has as its main purpose to record all communications that occur within the system, both between microservices and with external services.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>AU_11, AU_08, AU_09, AU_10, AU_12</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>communication log, leader, portal, access control, scheduler</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>CF_M05_AU23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Communication Log's main purpose is to record all communications that occur within the system, both between microservices and with external services.</t>
+        </is>
+      </c>
       <c r="L6" t="n">
-        <v>0.7501</v>
+        <v>0.9822</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -753,84 +741,36 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>The Leader microservice routes all communications to the corresponding microservice within the system architecture.</t>
+          <t>The user accesses the portal and applications.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>48,57</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_08, AU_09, AU_10, AU_11, AU_12</t>
+          <t>AU_01, AU_09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>leader, portal, access control, communication log, scheduler</t>
+          <t>user, portal</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CF_M05_AU22</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>CF_M05_AU02</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Portal Microservice</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
-        <is>
-          <t>Leader's main function is to route all communications to the corresponding microservice within the system architecture.</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>0.9520999999999999</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>AU_26</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>The portal microservice incorporates the binaries necessary for the frontEnd of both the portal itself and the rest of the portal applications.</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>AU_09, AU_13, AU_14, AU_15</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>portal, view, viewmodel, model</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>CF_M05_AU02</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Portal Microservice</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve">The portal microservice's main function is to provide a centralized interface for accessing the different VWGS
 applications. This component acts as an entry point for users, providing a unified experience. In addition to its
@@ -838,14 +778,68 @@
 itself and the rest of the portal's applications. </t>
         </is>
       </c>
+      <c r="L7" t="n">
+        <v>0.7501</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AU_25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>The presentation layer (Controllers) processes the requests received, manages the validation of the information and channels the requests to the corresponding modules or services of the data layer.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>AU_03, AU_04</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>presentation layer, business logic layer</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>CF_M05_AU17</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Presentation Layer (Controllers)</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>The controllers, through specific
+functions, process the requests received, manage the validation of the information and channel
+the requests to the corresponding modules or services of the data layer.</t>
+        </is>
+      </c>
       <c r="L8" t="n">
-        <v>0.8185</v>
+        <v>0.8548</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_28</t>
+          <t>AU_27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -856,97 +850,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>The services are responsible for orchestrating HTTP calls to the server.</t>
+          <t>The data access layer (Repositories) is responsible for performing queries on the database.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AU_14, AU_16</t>
+          <t>AU_05, AU_06</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>viewmodel, controller</t>
+          <t>data access layer, domain layer</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CF_M05_AU31</t>
+          <t>CF_M05_AU21</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>Data access layer (Repositories)</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>The message
-exchange protocol used in this case is HTTP</t>
+          <t>the Repositories are responsible for performing queries on the database.</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.7796999999999999</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>AU_29</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Controllers process received requests, manage validation, and channel requests to the data layer.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>AU_16, AU_04</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>controller, business logic layer</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>CF_M05_AU17</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Presentation Layer (Controllers)</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>The controllers, through specific
-functions, process the requests received, manage the validation of the information and channel
-the requests to the corresponding modules or services of the data layer.</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>0.7791</v>
+        <v>0.9316</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M05_arch_eval_llm_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M05_arch_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,7 +496,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The administrator is a user with additional permissions to manage application access for users.</t>
+          <t>The administrator is a user with additional permissions to manage application access.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -530,7 +530,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -545,7 +545,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>The data format used for communication.</t>
+          <t>The data format used is JSON.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -600,7 +600,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_08, AU_09, AU_10, AU_11, AU_12</t>
+          <t>AU_07, AU_08, AU_09, AU_10, AU_11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -638,51 +638,44 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>The portal microservice has as its main function to offer a centralized interface for access to the different VWGS applications. [...] This component acts as an entry point for users, providing a unified experience.</t>
+          <t>The portal microservice has as its main function to offer a centralized interface for access to the different VWGS applications. [...] In each portal, the relevant authentication and authorization controls are carried out with the help of the Leader which decides to which functional domain each user should be routed.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>57,60</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU_09, AU_08, AU_10, AU_11, AU_12</t>
+          <t>AU_08, AU_07</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>portal, leader, access control, communication log, scheduler</t>
+          <t>portal, leader</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CF_M05_AU02</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Portal Microservice</t>
-        </is>
-      </c>
+          <t>CF_M05_AU22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">The portal microservice's main function is to provide a centralized interface for accessing the different VWGS
-applications. This component acts as an entry point for users, providing a unified experience. In addition to its
-function as a portal, this microservice incorporates the necessary binaries for the frontEnd of both the portal
-itself and the rest of the portal's applications. </t>
+          <t>Leader's main function is to route all communications to the corresponding microservice within the system architecture.</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.8241000000000001</v>
+        <v>0.825</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -703,7 +696,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AU_11, AU_08, AU_09, AU_10, AU_12</t>
+          <t>AU_10, AU_07, AU_08, AU_09, AU_11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -741,51 +734,48 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>The user accesses the portal and applications.</t>
+          <t>The services offer the interface and the implementation of all the business logic of the application. [...] these call the corresponding functions to obtain the result of the request.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>48,57</t>
+          <t>69</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_01, AU_09</t>
+          <t>AU_04, AU_05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>user, portal</t>
+          <t>business logic layer, data access layer</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CF_M05_AU02</t>
+          <t>CF_M05_AU18</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Portal Microservice</t>
+          <t>Business Logic Layer (Services)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">The portal microservice's main function is to provide a centralized interface for accessing the different VWGS
-applications. This component acts as an entry point for users, providing a unified experience. In addition to its
-function as a portal, this microservice incorporates the necessary binaries for the frontEnd of both the portal
-itself and the rest of the portal's applications. </t>
+          <t>Services provide the interface and implementation of all the application's business logic.</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.7501</v>
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -796,96 +786,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>The presentation layer (Controllers) processes the requests received, manages the validation of the information and channels the requests to the corresponding modules or services of the data layer.</t>
+          <t>Finally, the Repositories are in charge of performing queries on the database.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>73</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AU_03, AU_04</t>
+          <t>AU_05, AU_06</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>presentation layer, business logic layer</t>
+          <t>data access layer, domain layer</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CF_M05_AU17</t>
+          <t>CF_M05_AU21</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Presentation Layer (Controllers)</t>
+          <t>Data access layer (Repositories)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>The controllers, through specific
-functions, process the requests received, manage the validation of the information and channel
-the requests to the corresponding modules or services of the data layer.</t>
+          <t>the Repositories are responsible for performing queries on the database.</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.8548</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>AU_27</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>The data access layer (Repositories) is responsible for performing queries on the database.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>AU_05, AU_06</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>data access layer, domain layer</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>CF_M05_AU21</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Data access layer (Repositories)</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>the Repositories are responsible for performing queries on the database.</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>0.9316</v>
+        <v>0.7919</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M05_arch_eval_llm_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M05_arch_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,7 +454,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>LLM_fixes</t>
+          <t>LLM_fixedType</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -481,12 +481,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>User</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -496,12 +496,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The administrator is a user with additional permissions to manage application access.</t>
+          <t>The user is the actor who accesses the portal and applications.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -509,48 +509,49 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CF_M05_AU32</t>
+          <t>CF_M05_AU13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Server (Backend)</t>
+          <t>View</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
-responsibilities are separated:</t>
+          <t>The component we call View, Vista in Catalan, is made up of the HTML and SCSS files of
+each component that makes up the application. They are responsible for presenting the
+screens and capturing user interactions such as clicks or text entries.</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.6979</v>
+        <v>0.7551</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JSON</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>The data format used is JSON.</t>
+          <t>The administrator is a user with additional permissions to assign or revoke access to applications.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>47, 50</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -558,270 +559,431 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
+          <t>CF_M05_AU32</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Server (Backend)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
+responsibilities are separated:</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.6979</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AU_13</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>The client, which we also call frontEnd, is responsible for the presentation and user experience of the application.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>P_03</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>CF_M05_AU06</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Client(Frontend)</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>The client, also called the frontEnd, is responsible for the presentation and user experience
+of the application by encapsulating the interface logic and coordinating the calls to the server
+API.</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.8573</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AU_14</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>For the server, the backEnd, Spring Boot organizes the code following the layered pattern.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>P_03, P_05</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>CF_M05_AU32</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Server (Backend)</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
+responsibilities are separated:</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.9097</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AU_18</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>The data format used is JSON.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>AU_14, AU_23</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>CF_M05_AU31</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>HTTP</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>The message
 exchange protocol used in this case is HTTP</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="L6" t="n">
         <v>0.678</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AU_18</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>The Leader microservice has as its main function the routing of all communications to the corresponding microservice within the system architecture.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>AU_07, AU_08, AU_09, AU_10, AU_11</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>leader, portal, access control, communication log, scheduler</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>CF_M05_AU22</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Leader's main function is to route all communications to the corresponding microservice within the system architecture.</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>0.9671</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AU_19</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>The portal microservice has as its main function to offer a centralized interface for access to the different VWGS applications. [...] In each portal, the relevant authentication and authorization controls are carried out with the help of the Leader which decides to which functional domain each user should be routed.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>57,60</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>AU_08, AU_07</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>portal, leader</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>CF_M05_AU22</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Leader's main function is to route all communications to the corresponding microservice within the system architecture.</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>0.825</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AU_20</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>The Communication Log microservice has as its main purpose to record all communications that occur within the system, both between microservices and with external services.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>AU_10, AU_07, AU_08, AU_09, AU_11</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>communication log, leader, portal, access control, scheduler</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>CF_M05_AU23</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Communication Log's main purpose is to record all communications that occur within the system, both between microservices and with external services.</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>0.9822</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_23</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>AU_19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Amazon Web Services</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>The services offer the interface and the implementation of all the business logic of the application. [...] these call the corresponding functions to obtain the result of the request.</t>
+          <t>The provider for this project is Amazon Web Services.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>AU_04, AU_05</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>business logic layer, data access layer</t>
-        </is>
-      </c>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CF_M05_AU18</t>
+          <t>CF_M05_AU10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Business Logic Layer (Services)</t>
+          <t>Amazon RDS</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Services provide the interface and implementation of all the application's business logic.</t>
+          <t xml:space="preserve"> the microservices are connected to a shared database (Amazon RDS) that is decoupled per
+microservice and client. </t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8105</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_24</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>AU_20</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kubernetes</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Finally, the Repositories are in charge of performing queries on the database.</t>
+          <t>Kubernetes is a container orchestration platform used for deployment.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AU_05, AU_06</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>data access layer, domain layer</t>
-        </is>
-      </c>
+          <t>AU_19</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
+          <t>CF_M05_AU33</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Docker</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>The deployment process for our application begins with the creation of a Docker image [28] for each microservice which has its own repository with a Dockerfile [29].</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0.7665</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AU_21</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>The Leader microservice has as its main function the routing of all communications to the corresponding microservice within the system architecture.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>AU_08, AU_09, AU_10, AU_11, AU_12</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>leader, portal, access control, communication log, scheduler</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>CF_M05_AU22</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Leader's main function is to route all communications to the corresponding microservice within the system architecture.</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0.9671</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AU_23</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>The communication between the two components [client and server] is done through an exchange of messages following standard network protocols and using interoperable data representation formats.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>AU_13, AU_14</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>frontend, backend</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>CF_M05_AU24</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Communication between the two components [client-server] is done through an exchange of messages following standard network protocols and making use of interoperable data representation formats.</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0.9965000000000001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AU_24</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>The data access layer interacts with the database.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>AU_05, AU_14</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>data access layer, backend</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>CF_M05_AU21</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Data access layer (Repositories)</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>the Repositories are responsible for performing queries on the database.</t>
         </is>
       </c>
-      <c r="L8" t="n">
-        <v>0.7919</v>
+      <c r="L11" t="n">
+        <v>0.8915</v>
       </c>
     </row>
   </sheetData>
